--- a/4_screener/control_file_screener.xlsx
+++ b/4_screener/control_file_screener.xlsx
@@ -1,23 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vub-my.sharepoint.com/personal/sebastian_sterl_vub_be/Documents/Documenten/VUB Work Files/MSR code repo/4_screener/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_45D1994FA523C4CCDB0E93F53221E29A06D19D57" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8F2EA96-7FFD-4CAD-911B-05E664ADC67D}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="paths"/>
-    <sheet r:id="rId2" sheetId="2" name="parameters"/>
-    <sheet r:id="rId3" sheetId="3" name="configurations"/>
-    <sheet r:id="rId4" sheetId="4" name="datasets"/>
+    <sheet name="paths" sheetId="1" r:id="rId1"/>
+    <sheet name="parameters" sheetId="2" r:id="rId2"/>
+    <sheet name="configurations" sheetId="3" r:id="rId3"/>
+    <sheet name="datasets" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="33">
   <si>
     <t>datasets</t>
   </si>
@@ -106,20 +112,22 @@
     <t>C:\Dev\model_supply_regions\Model-Supply-Regions-MSR-Toolset\outputs\</t>
   </si>
   <si>
-    <t>Destination folder where screened results are placed. This folder will be created by script if it does not exist.</t>
-  </si>
-  <si>
     <t>input_folder_datasets</t>
   </si>
   <si>
     <t>C:\Users\mastt\OneDrive - VITO\Documents\21_WP1\RawData\model_supply_regions\workflow\inputs\2022 MSR Toolset Inputs\</t>
   </si>
+  <si>
+    <t>Folder path where input datasets are located.</t>
+  </si>
+  <si>
+    <t>Folder path where output files are located.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -190,88 +198,105 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C5" displayName="Table6" name="Table6" id="1" totalsRowShown="0">
-  <autoFilter ref="A1:C5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table4" displayName="Table4" ref="A1:C3" totalsRowShown="0">
+  <autoFilter ref="A1:C3" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="3">
-    <tableColumn name="datasets" id="1"/>
-    <tableColumn name="value" id="2"/>
-    <tableColumn name="comments" id="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="parameters"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="value"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="comments" dataDxfId="0"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C9" displayName="Table3" name="Table3" id="2" totalsRowShown="0">
-  <autoFilter ref="A1:C9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table3" displayName="Table3" ref="A1:C9" totalsRowShown="0">
+  <autoFilter ref="A1:C9" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="3">
-    <tableColumn name="parameter" id="1"/>
-    <tableColumn name="value" id="2"/>
-    <tableColumn name="comments" id="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="parameter"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="value"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="comments"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C3" displayName="Table4" name="Table4" id="3" totalsRowShown="0">
-  <autoFilter ref="A1:C3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table6" displayName="Table6" ref="A1:C5" totalsRowShown="0">
+  <autoFilter ref="A1:C5" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
-    <tableColumn name="parameters" id="1"/>
-    <tableColumn name="value" id="2"/>
-    <tableColumn name="comments" id="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="datasets"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="value"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="comments"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -280,10 +305,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -321,71 +346,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -413,7 +438,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -436,11 +461,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -449,13 +474,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -465,7 +490,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -474,7 +499,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -483,7 +508,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -491,10 +516,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -559,49 +584,49 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" style="11" width="53.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="11" width="46.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="11" width="43.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="53.26953125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.7265625" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5" customFormat="1" s="8">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3" s="6" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="46.5" customFormat="1" s="8">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:3" s="6" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" s="6" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="60" customFormat="1" s="8">
-      <c r="A3" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>5</v>
+      <c r="C3" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -613,48 +638,48 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" style="2" width="66.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="13.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="2" width="13.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="17.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="1">
         <v>100</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="5">
         <v>3000</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>24</v>
       </c>
     </row>
@@ -664,114 +689,114 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" style="2" width="25.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="2" width="20.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="14.4">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="1">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="1">
         <v>0</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="1">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="1">
         <v>0</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="1">
         <v>0</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="1">
         <v>1</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="1">
         <v>1</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="1">
         <v>1</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>14</v>
       </c>
     </row>
@@ -784,66 +809,63 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="2" width="11.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="1" t="s">
+    </row>
+    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="1" t="s">
+    </row>
+    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/4_screener/control_file_screener.xlsx
+++ b/4_screener/control_file_screener.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vub-my.sharepoint.com/personal/sebastian_sterl_vub_be/Documents/Documenten/VUB Work Files/MSR code repo/4_screener/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vub-my.sharepoint.com/personal/sebastian_sterl_vub_be/Documents/Documenten/VUB Work Files/26001 MSR tutorial/4_screener/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_45D1994FA523C4CCDB0E93F53221E29A06D19D57" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8F2EA96-7FFD-4CAD-911B-05E664ADC67D}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="11_80B9B95D81B3C9CA172E92C8EAA3E9A4C6D1516A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D834B5E-2192-48D3-A511-DB8123E465CD}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="paths" sheetId="1" r:id="rId1"/>
-    <sheet name="parameters" sheetId="2" r:id="rId2"/>
+    <sheet name="datasets" sheetId="4" r:id="rId2"/>
     <sheet name="configurations" sheetId="3" r:id="rId3"/>
-    <sheet name="datasets" sheetId="4" r:id="rId4"/>
+    <sheet name="parameters" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
   <si>
     <t>datasets</t>
   </si>
@@ -37,12 +37,6 @@
     <t>region_boundaries</t>
   </si>
   <si>
-    <t>AllCountryBoundaries_GAUL.shp</t>
-  </si>
-  <si>
-    <t>Address to region boundaries shapefile</t>
-  </si>
-  <si>
     <t>regions</t>
   </si>
   <si>
@@ -94,41 +88,63 @@
     <t>add_cf_profiles</t>
   </si>
   <si>
-    <t>wind_hub_height</t>
-  </si>
-  <si>
-    <t>Unit: m</t>
-  </si>
-  <si>
-    <t>elevation_threshold</t>
-  </si>
-  <si>
     <t>parameters</t>
   </si>
   <si>
     <t>output_folder</t>
   </si>
   <si>
-    <t>C:\Dev\model_supply_regions\Model-Supply-Regions-MSR-Toolset\outputs\</t>
-  </si>
-  <si>
     <t>input_folder_datasets</t>
   </si>
   <si>
-    <t>C:\Users\mastt\OneDrive - VITO\Documents\21_WP1\RawData\model_supply_regions\workflow\inputs\2022 MSR Toolset Inputs\</t>
+    <t>C:\Users\adm_sesterl\OneDrive - Vrije Universiteit Brussel\Documenten\VUB Work Files\26001 MSR tutorial\outputs</t>
+  </si>
+  <si>
+    <t>C:\Users\adm_sesterl\OneDrive - Vrije Universiteit Brussel\Documenten\VUB Work Files\26001 MSR tutorial\inputs</t>
+  </si>
+  <si>
+    <t>Ecuador.shp</t>
   </si>
   <si>
     <t>Folder path where input datasets are located.</t>
   </si>
   <si>
     <t>Folder path where output files are located.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Options=[0-No, 1-Yes]. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Not yet operational - for future use</t>
+    </r>
+  </si>
+  <si>
+    <t>Name of region names table (input folder)</t>
+  </si>
+  <si>
+    <t>Name of region boundaries shapefile (input folder)</t>
+  </si>
+  <si>
+    <t>Name of regional area cutoff thresholds (input folder) for solar PV</t>
+  </si>
+  <si>
+    <t>Name of regional area cutoff thresholds (input folder) for wind</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,9 +167,36 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -198,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -212,9 +255,6 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -226,12 +266,23 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <font>
         <b val="0"/>
@@ -251,6 +302,20 @@
       </font>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -264,12 +329,16 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table4" displayName="Table4" ref="A1:C3" totalsRowShown="0">
   <autoFilter ref="A1:C3" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="parameters"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="value"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="value" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="comments" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -277,24 +346,24 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table6" displayName="Table6" ref="A1:C5" totalsRowShown="0">
+  <autoFilter ref="A1:C5" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="datasets"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="value"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="comments"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table3" displayName="Table3" ref="A1:C9" totalsRowShown="0">
   <autoFilter ref="A1:C9" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="parameter"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="value"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="comments"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table6" displayName="Table6" ref="A1:C5" totalsRowShown="0">
-  <autoFilter ref="A1:C5" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="datasets"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="value"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="comments"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -591,42 +660,42 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="53.26953125" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.453125" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.7265625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.453125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.7265625" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="6" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="7" t="s">
+    <row r="1" spans="1:3" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="6" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" s="6" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
+    <row r="2" spans="1:3" s="5" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="8" t="s">
+    </row>
+    <row r="3" spans="1:3" s="5" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -638,11 +707,203 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="28.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="56.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="29.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="11">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="11">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="11">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="11">
+        <v>0</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="13"/>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.6328125" bestFit="1" customWidth="1"/>
@@ -652,225 +913,16 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="1">
-        <v>100</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="5">
-        <v>3000</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.26953125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="1">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="1">
-        <v>0</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="1">
-        <v>0</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="1">
-        <v>0</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="1">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="1">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="1">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>